--- a/data/trans_dic/IP1020-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos crónicos de la piel</t>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,66</t>
+          <t>0,52; 5,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,52</t>
+          <t>1,17; 8,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,32</t>
+          <t>0,41; 4,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,33</t>
+          <t>0,44; 4,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,92</t>
+          <t>0,25; 2,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,84</t>
+          <t>0,8; 3,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,3</t>
+          <t>0,23; 2,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,19</t>
+          <t>0,99; 4,44</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,66</t>
+          <t>0,63; 3,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,28</t>
+          <t>1,35; 5,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,04</t>
+          <t>0,83; 4,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,32</t>
+          <t>1,3; 5,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,14</t>
+          <t>0,92; 4,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,41</t>
+          <t>0,58; 3,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,77</t>
+          <t>2,92; 7,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,21</t>
+          <t>1,1; 3,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,99</t>
+          <t>0,91; 2,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,13</t>
+          <t>0,89; 3,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,89</t>
+          <t>2,52; 5,68</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,74</t>
+          <t>0,95; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,81</t>
+          <t>0,66; 3,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,88</t>
+          <t>2,18; 7,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,61</t>
+          <t>0,42; 3,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,45</t>
+          <t>0,99; 4,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,96</t>
+          <t>0,69; 2,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,08</t>
+          <t>0,78; 2,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,48</t>
+          <t>1,97; 5,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,59</t>
+          <t>1,16; 5,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,88</t>
+          <t>0,33; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,48</t>
+          <t>1,27; 5,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,3</t>
+          <t>1,26; 5,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,35</t>
+          <t>0,93; 4,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,38</t>
+          <t>1,8; 6,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,36</t>
+          <t>0,16; 1,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,43</t>
+          <t>1,56; 4,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,97</t>
+          <t>0,82; 3,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,0</t>
+          <t>1,77; 5,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,68</t>
+          <t>1,73; 3,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,18</t>
+          <t>0,78; 2,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,85</t>
+          <t>2,35; 4,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,55</t>
+          <t>0,45; 1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,23</t>
+          <t>0,79; 2,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,79</t>
+          <t>0,97; 2,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,53</t>
+          <t>2,29; 4,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,29</t>
+          <t>0,5; 1,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,61</t>
+          <t>1,4; 2,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,12</t>
+          <t>1,06; 2,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,21</t>
+          <t>2,54; 4,19</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5090</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>703; 7057</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1377; 9437</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>631; 6750</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>648; 6701</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>353; 4183</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4366</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2327; 11228</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>651; 7517</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2553; 11441</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12430</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7792</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7675</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>17741</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1226; 7047</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2769; 10525</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1730; 8491</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2467; 10822</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1959; 9284</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4670</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1295; 6754</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7434; 19834</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4483; 13551</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3903; 12642</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3839; 13039</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>11230; 25321</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4384</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12725</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1471; 7778</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1025; 5917</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4142; 14936</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2556</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4185</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>692; 6250</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1834; 9241</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2428</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2205; 9588</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2529; 9648</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7390; 19337</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5632</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4586</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5574</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6468</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11207</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6722</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>11054</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2434; 10757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>681; 6552</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2128; 9206</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4671</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2608; 10567</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1913; 10147</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3256; 11950</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>650; 5583</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6508; 18178</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3384; 12446</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6172; 17596</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18278</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9273</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>24771</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11840</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28751</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>47102</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2517; 10293</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12212; 26476</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5460; 15438</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15613; 32889</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3276; 12282</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5933; 17055</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7258; 19103</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17429; 34768</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6964; 18898</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20404; 38533</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15338; 30510</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>36197; 59866</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1020-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Habitat-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,17</t>
+          <t>0,51; 5,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,05</t>
+          <t>1,14; 8,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,53</t>
+          <t>0,43; 4,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,98</t>
+          <t>0,26; 2,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,88</t>
+          <t>0,81; 3,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,67</t>
+          <t>0,23; 2,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,44</t>
+          <t>0,94; 4,61</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,61</t>
+          <t>0,63; 3,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,12</t>
+          <t>1,27; 5,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,1</t>
+          <t>0,87; 3,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,68</t>
+          <t>1,19; 5,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,01</t>
+          <t>0,59; 3,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,78</t>
+          <t>2,94; 8,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,33</t>
+          <t>1,09; 3,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,96</t>
+          <t>0,96; 3,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,02</t>
+          <t>0,91; 3,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,68</t>
+          <t>2,72; 5,9</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,02</t>
+          <t>0,91; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,79</t>
+          <t>0,68; 3,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,88</t>
+          <t>2,11; 7,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,75</t>
+          <t>0,42; 3,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,99</t>
+          <t>1,08; 5,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,99</t>
+          <t>0,72; 2,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,99</t>
+          <t>0,82; 3,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,16</t>
+          <t>1,93; 5,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,12</t>
+          <t>1,17; 5,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,16</t>
+          <t>0,33; 2,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,48</t>
+          <t>1,13; 5,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,1</t>
+          <t>1,29; 4,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,93</t>
+          <t>0,85; 4,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,59</t>
+          <t>1,77; 6,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,34</t>
+          <t>0,16; 1,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,36</t>
+          <t>1,5; 4,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,01</t>
+          <t>0,66; 2,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,04</t>
+          <t>1,81; 5,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,51</t>
+          <t>0,38; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,75</t>
+          <t>1,66; 3,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,19</t>
+          <t>0,76; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,94</t>
+          <t>2,22; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,7</t>
+          <t>0,46; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,28</t>
+          <t>0,79; 2,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,56</t>
+          <t>1,03; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,56</t>
+          <t>2,25; 4,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,35</t>
+          <t>0,52; 1,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,65</t>
+          <t>1,47; 2,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,11</t>
+          <t>1,09; 2,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,19</t>
+          <t>2,56; 4,18</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 5485</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>703; 7057</t>
+          <t>695; 7486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1377; 9437</t>
+          <t>1342; 9687</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>631; 6750</t>
+          <t>629; 6749</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>648; 6701</t>
+          <t>644; 6227</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>353; 4183</t>
+          <t>368; 4090</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4366</t>
+          <t>0; 5094</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2327; 11228</t>
+          <t>2353; 10822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651; 7517</t>
+          <t>649; 7141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2553; 11441</t>
+          <t>2434; 11887</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1226; 7047</t>
+          <t>1227; 6995</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2769; 10525</t>
+          <t>2617; 10525</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1730; 8491</t>
+          <t>1796; 8144</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2467; 10822</t>
+          <t>2270; 9860</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1959; 9284</t>
+          <t>1949; 9292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1295; 6754</t>
+          <t>1322; 7425</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7434; 19834</t>
+          <t>7489; 21349</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4483; 13551</t>
+          <t>4455; 13631</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3903; 12642</t>
+          <t>4094; 12841</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3839; 13039</t>
+          <t>3921; 13401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11230; 25321</t>
+          <t>12126; 26296</t>
         </is>
       </c>
     </row>
@@ -2066,57 +2066,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1471; 7778</t>
+          <t>1410; 7563</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1025; 5917</t>
+          <t>1055; 6178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4142; 14936</t>
+          <t>4005; 15079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2556</t>
+          <t>0; 2649</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4014</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>692; 6250</t>
+          <t>697; 6133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1834; 9241</t>
+          <t>1996; 9624</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2428</t>
+          <t>0; 2438</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2205; 9588</t>
+          <t>2307; 9566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2529; 9648</t>
+          <t>2634; 9927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7390; 19337</t>
+          <t>7227; 19895</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4145</t>
+          <t>0; 3909</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2434; 10757</t>
+          <t>2457; 11656</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>681; 6552</t>
+          <t>685; 6200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2128; 9206</t>
+          <t>1892; 9215</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4671</t>
+          <t>0; 4765</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2608; 10567</t>
+          <t>2671; 10158</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1913; 10147</t>
+          <t>1751; 9539</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3256; 11950</t>
+          <t>3206; 12535</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>650; 5583</t>
+          <t>650; 5683</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6508; 18178</t>
+          <t>6265; 17448</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3384; 12446</t>
+          <t>2747; 11919</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6172; 17596</t>
+          <t>6329; 18657</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2517; 10293</t>
+          <t>2582; 10688</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12212; 26476</t>
+          <t>11700; 25770</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5460; 15438</t>
+          <t>5346; 15234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15613; 32889</t>
+          <t>14743; 31410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3276; 12282</t>
+          <t>3307; 11581</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5933; 17055</t>
+          <t>5931; 16942</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7258; 19103</t>
+          <t>7657; 19954</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17429; 34768</t>
+          <t>17113; 34309</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6964; 18898</t>
+          <t>7264; 18556</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20404; 38533</t>
+          <t>21325; 40005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15338; 30510</t>
+          <t>15728; 31162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36197; 59866</t>
+          <t>36581; 59673</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1020-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,49</t>
+          <t>0,41; 4,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,43; 4,33</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,2; 3,06</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,04</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,52; 5,66</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 8,26</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,41; 4,41</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,43; 4,21</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,91</t>
+          <t>1,26; 8,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,74</t>
+          <t>0,82; 3,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,53</t>
+          <t>0,23; 2,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,61</t>
+          <t>1,02; 4,69</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,58</t>
+          <t>0,96; 4,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,12</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,93</t>
+          <t>0,59; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,18</t>
+          <t>2,89; 8,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,38</t>
+          <t>0,63; 3,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>1,47; 5,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,31</t>
+          <t>0,86; 4,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,37</t>
+          <t>1,29; 5,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,35</t>
+          <t>1,01; 3,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,0</t>
+          <t>0,94; 2,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,1</t>
+          <t>1,01; 3,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,9</t>
+          <t>2,68; 5,96</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -997,42 +997,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,33</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,4; 3,61</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,18; 6,06</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 4,88</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 3,96</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2,11; 7,95</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,77</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,8; 4,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,68</t>
+          <t>0,59; 3,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,19</t>
+          <t>2,92; 9,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,98</t>
+          <t>0,65; 2,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,08</t>
+          <t>0,77; 3,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,31</t>
+          <t>2,55; 6,39</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1,3; 5,3</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,66; 4,35</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,65; 6,57</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,87</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 5,54</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,33; 2,99</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 5,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,29</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,91</t>
+          <t>1,18; 5,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,64</t>
+          <t>0,33; 2,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,92</t>
+          <t>1,24; 5,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,18</t>
+          <t>1,52; 4,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,88</t>
+          <t>0,77; 2,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,34</t>
+          <t>1,81; 5,09</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,57</t>
+          <t>0,45; 1,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,65</t>
+          <t>0,78; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,16</t>
+          <t>1,03; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,72</t>
+          <t>2,35; 4,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,6</t>
+          <t>0,31; 1,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,26</t>
+          <t>1,72; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,68</t>
+          <t>0,75; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,5</t>
+          <t>2,51; 5,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,32</t>
+          <t>0,52; 1,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,75</t>
+          <t>1,46; 2,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,15</t>
+          <t>1,09; 2,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,18</t>
+          <t>2,66; 4,49</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1452</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3066</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4092</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2275</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5418</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5710</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5485</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>695; 7486</t>
+          <t>632; 6621</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>643; 6419</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>253; 3858</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5607</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>704; 7721</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1342; 9687</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>629; 6749</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>644; 6227</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>368; 4090</t>
+          <t>1522; 10881</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5094</t>
+          <t>0; 4588</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2353; 10822</t>
+          <t>2363; 11115</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>649; 7141</t>
+          <t>653; 6473</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2434; 11887</t>
+          <t>2513; 11593</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11774</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5906</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4326</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4634</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17032</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1227; 6995</t>
+          <t>2028; 8785</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2617; 10525</t>
+          <t>0; 5364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1796; 8144</t>
+          <t>1316; 7643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2270; 9860</t>
+          <t>6846; 19370</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1949; 9292</t>
+          <t>1232; 7152</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4992</t>
+          <t>3015; 10853</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1322; 7425</t>
+          <t>1781; 8373</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7489; 21349</t>
+          <t>2375; 10067</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4455; 13631</t>
+          <t>4127; 13073</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4094; 12841</t>
+          <t>4000; 12779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3921; 13401</t>
+          <t>4369; 13492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12126; 26296</t>
+          <t>11295; 25138</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3673</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2695</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8342</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4384</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>4786</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>13305</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 2430</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3862</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>668; 6025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1994; 10209</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1410; 7563</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1055; 6178</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4005; 15079</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2649</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4014</t>
+          <t>1241; 7334</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>697; 6133</t>
+          <t>919; 5936</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1996; 9624</t>
+          <t>4563; 15376</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2438</t>
+          <t>0; 2435</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2307; 9566</t>
+          <t>2100; 9485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2634; 9927</t>
+          <t>2491; 9933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7227; 19895</t>
+          <t>8271; 20738</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5574</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4471</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2251</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4586</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5574</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10922</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3909</t>
+          <t>0; 4714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2457; 11656</t>
+          <t>2698; 10972</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>685; 6200</t>
+          <t>1356; 8942</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1892; 9215</t>
+          <t>2793; 11121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4765</t>
+          <t>0; 3910</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2671; 10158</t>
+          <t>2485; 11763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1751; 9539</t>
+          <t>677; 5975</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3206; 12535</t>
+          <t>2067; 9699</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>650; 5683</t>
+          <t>651; 5660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6265; 17448</t>
+          <t>6337; 18492</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2747; 11919</t>
+          <t>3182; 12260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6329; 18657</t>
+          <t>6106; 17129</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2582; 10688</t>
+          <t>3225; 11189</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11700; 25770</t>
+          <t>5802; 16679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5346; 15234</t>
+          <t>7671; 20758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14743; 31410</t>
+          <t>16439; 33216</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3307; 11581</t>
+          <t>2129; 10536</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5931; 16942</t>
+          <t>12126; 26014</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7657; 19954</t>
+          <t>5285; 15348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17113; 34309</t>
+          <t>15793; 33047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7264; 18556</t>
+          <t>7253; 18105</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21325; 40005</t>
+          <t>21301; 38030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15728; 31162</t>
+          <t>15747; 30705</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36581; 59673</t>
+          <t>35412; 59721</t>
         </is>
       </c>
     </row>
